--- a/data/satisfaction_detail/2026/6月/参展商.xlsx
+++ b/data/satisfaction_detail/2026/6月/参展商.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.42</v>
+        <v>9.52</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.970000000000001</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -540,7 +540,7 @@
         <v>9.75</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="8">
@@ -559,10 +559,10 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>9.15</v>
+        <v>9.16</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>9.9</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>8.130000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>10</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>9.449999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>9.92</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>9.050000000000001</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="13">
@@ -611,10 +611,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>9.25</v>
+        <v>9.24</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>9.83</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9.210000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.83</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -637,10 +637,10 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>9.17</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>10</v>
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>10</v>
